--- a/SH1001 intensities.xlsx
+++ b/SH1001 intensities.xlsx
@@ -7,9 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1001 Ebba680+ R2 airyscan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1001 Ebba680+ R3 airyscan" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1001 Ebba680+ R1 airyscan" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1001 Ebba680+ R1 airy" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1001 Ebba680+ R2 airy" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SH1001 Ebba680+ R3 airy" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -447,10 +447,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7505043</v>
+        <v>11120035</v>
       </c>
       <c r="C2" t="n">
-        <v>17384</v>
+        <v>21545</v>
       </c>
     </row>
     <row r="3">
@@ -458,10 +458,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7589573</v>
+        <v>11151489</v>
       </c>
       <c r="C3" t="n">
-        <v>15963</v>
+        <v>22025</v>
       </c>
     </row>
     <row r="4">
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>7732794</v>
+        <v>11722767</v>
       </c>
       <c r="C4" t="n">
-        <v>16360</v>
+        <v>23958</v>
       </c>
     </row>
     <row r="5">
@@ -480,10 +480,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>7877427</v>
+        <v>12091313</v>
       </c>
       <c r="C5" t="n">
-        <v>17736</v>
+        <v>25665</v>
       </c>
     </row>
     <row r="6">
@@ -491,10 +491,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8182906</v>
+        <v>12916903</v>
       </c>
       <c r="C6" t="n">
-        <v>18604</v>
+        <v>27293</v>
       </c>
     </row>
     <row r="7">
@@ -502,10 +502,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8257774</v>
+        <v>13371175</v>
       </c>
       <c r="C7" t="n">
-        <v>19199</v>
+        <v>28864</v>
       </c>
     </row>
     <row r="8">
@@ -513,10 +513,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8506695</v>
+        <v>13846567</v>
       </c>
       <c r="C8" t="n">
-        <v>20513</v>
+        <v>31744</v>
       </c>
     </row>
     <row r="9">
@@ -524,10 +524,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8784924</v>
+        <v>14619637</v>
       </c>
       <c r="C9" t="n">
-        <v>20501</v>
+        <v>32160</v>
       </c>
     </row>
     <row r="10">
@@ -535,10 +535,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9141904</v>
+        <v>15181894</v>
       </c>
       <c r="C10" t="n">
-        <v>22175</v>
+        <v>33764</v>
       </c>
     </row>
     <row r="11">
@@ -546,10 +546,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9236781</v>
+        <v>15739583</v>
       </c>
       <c r="C11" t="n">
-        <v>22893</v>
+        <v>36875</v>
       </c>
     </row>
     <row r="12">
@@ -557,10 +557,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9447614</v>
+        <v>16582982</v>
       </c>
       <c r="C12" t="n">
-        <v>21136</v>
+        <v>39661</v>
       </c>
     </row>
     <row r="13">
@@ -568,10 +568,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9718024</v>
+        <v>17676142</v>
       </c>
       <c r="C13" t="n">
-        <v>23040</v>
+        <v>43460</v>
       </c>
     </row>
     <row r="14">
@@ -579,10 +579,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>10124829</v>
+        <v>18940932</v>
       </c>
       <c r="C14" t="n">
-        <v>23804</v>
+        <v>49436</v>
       </c>
     </row>
     <row r="15">
@@ -590,10 +590,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>10638135</v>
+        <v>21243715</v>
       </c>
       <c r="C15" t="n">
-        <v>26600</v>
+        <v>55599</v>
       </c>
     </row>
     <row r="16">
@@ -601,10 +601,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11137363</v>
+        <v>23324792</v>
       </c>
       <c r="C16" t="n">
-        <v>27737</v>
+        <v>66375</v>
       </c>
     </row>
     <row r="17">
@@ -612,10 +612,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11806549</v>
+        <v>26374060</v>
       </c>
       <c r="C17" t="n">
-        <v>30858</v>
+        <v>76193</v>
       </c>
     </row>
     <row r="18">
@@ -623,10 +623,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12183493</v>
+        <v>30504776</v>
       </c>
       <c r="C18" t="n">
-        <v>31699</v>
+        <v>88625</v>
       </c>
     </row>
     <row r="19">
@@ -634,10 +634,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12653166</v>
+        <v>33682533</v>
       </c>
       <c r="C19" t="n">
-        <v>33388</v>
+        <v>104345</v>
       </c>
     </row>
     <row r="20">
@@ -645,10 +645,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>13530055</v>
+        <v>39447744</v>
       </c>
       <c r="C20" t="n">
-        <v>37164</v>
+        <v>131242</v>
       </c>
     </row>
     <row r="21">
@@ -656,10 +656,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>14158035</v>
+        <v>47999504</v>
       </c>
       <c r="C21" t="n">
-        <v>38704</v>
+        <v>166459</v>
       </c>
     </row>
     <row r="22">
@@ -667,10 +667,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>15093161</v>
+        <v>62339911</v>
       </c>
       <c r="C22" t="n">
-        <v>44039</v>
+        <v>233632</v>
       </c>
     </row>
     <row r="23">
@@ -678,10 +678,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>16773919</v>
+        <v>78230154</v>
       </c>
       <c r="C23" t="n">
-        <v>48755</v>
+        <v>324565</v>
       </c>
     </row>
     <row r="24">
@@ -689,10 +689,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>18501071</v>
+        <v>90325773</v>
       </c>
       <c r="C24" t="n">
-        <v>53969</v>
+        <v>425281</v>
       </c>
     </row>
     <row r="25">
@@ -700,10 +700,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>20459044</v>
+        <v>101414078</v>
       </c>
       <c r="C25" t="n">
-        <v>64891</v>
+        <v>508923</v>
       </c>
     </row>
     <row r="26">
@@ -711,10 +711,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>22324829</v>
+        <v>109030262</v>
       </c>
       <c r="C26" t="n">
-        <v>68294</v>
+        <v>570215</v>
       </c>
     </row>
     <row r="27">
@@ -722,10 +722,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>24032653</v>
+        <v>115266889</v>
       </c>
       <c r="C27" t="n">
-        <v>78841</v>
+        <v>631954</v>
       </c>
     </row>
     <row r="28">
@@ -733,10 +733,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>26018307</v>
+        <v>119421198</v>
       </c>
       <c r="C28" t="n">
-        <v>85446</v>
+        <v>666254</v>
       </c>
     </row>
     <row r="29">
@@ -744,10 +744,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>28718034</v>
+        <v>124347187</v>
       </c>
       <c r="C29" t="n">
-        <v>96919</v>
+        <v>698950</v>
       </c>
     </row>
     <row r="30">
@@ -755,10 +755,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>33144327</v>
+        <v>128305735</v>
       </c>
       <c r="C30" t="n">
-        <v>113922</v>
+        <v>709271</v>
       </c>
     </row>
     <row r="31">
@@ -766,10 +766,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>39377612</v>
+        <v>132597747</v>
       </c>
       <c r="C31" t="n">
-        <v>141364</v>
+        <v>724329</v>
       </c>
     </row>
     <row r="32">
@@ -777,10 +777,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>50844565</v>
+        <v>135252053</v>
       </c>
       <c r="C32" t="n">
-        <v>195920</v>
+        <v>737443</v>
       </c>
     </row>
     <row r="33">
@@ -788,10 +788,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>65020692</v>
+        <v>136744605</v>
       </c>
       <c r="C33" t="n">
-        <v>267695</v>
+        <v>743589</v>
       </c>
     </row>
     <row r="34">
@@ -799,10 +799,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>77518626</v>
+        <v>137869222</v>
       </c>
       <c r="C34" t="n">
-        <v>356885</v>
+        <v>750826</v>
       </c>
     </row>
     <row r="35">
@@ -810,10 +810,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>87971277</v>
+        <v>138199553</v>
       </c>
       <c r="C35" t="n">
-        <v>446437</v>
+        <v>747429</v>
       </c>
     </row>
     <row r="36">
@@ -821,10 +821,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>97314744</v>
+        <v>138524853</v>
       </c>
       <c r="C36" t="n">
-        <v>534462</v>
+        <v>748240</v>
       </c>
     </row>
     <row r="37">
@@ -832,10 +832,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>105459259</v>
+        <v>138811607</v>
       </c>
       <c r="C37" t="n">
-        <v>602037</v>
+        <v>752192</v>
       </c>
     </row>
     <row r="38">
@@ -843,10 +843,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>111585290</v>
+        <v>139229583</v>
       </c>
       <c r="C38" t="n">
-        <v>667327</v>
+        <v>739846</v>
       </c>
     </row>
     <row r="39">
@@ -854,10 +854,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>115277760</v>
+        <v>139198093</v>
       </c>
       <c r="C39" t="n">
-        <v>695596</v>
+        <v>737904</v>
       </c>
     </row>
     <row r="40">
@@ -865,10 +865,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>117596538</v>
+        <v>138754551</v>
       </c>
       <c r="C40" t="n">
-        <v>697153</v>
+        <v>728565</v>
       </c>
     </row>
     <row r="41">
@@ -876,10 +876,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>119159986</v>
+        <v>138037649</v>
       </c>
       <c r="C41" t="n">
-        <v>696260</v>
+        <v>726333</v>
       </c>
     </row>
     <row r="42">
@@ -887,10 +887,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>120121827</v>
+        <v>136897166</v>
       </c>
       <c r="C42" t="n">
-        <v>701437</v>
+        <v>722908</v>
       </c>
     </row>
     <row r="43">
@@ -898,10 +898,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>120631349</v>
+        <v>136609491</v>
       </c>
       <c r="C43" t="n">
-        <v>696200</v>
+        <v>714356</v>
       </c>
     </row>
     <row r="44">
@@ -909,10 +909,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>121200180</v>
+        <v>135705317</v>
       </c>
       <c r="C44" t="n">
-        <v>705483</v>
+        <v>709608</v>
       </c>
     </row>
     <row r="45">
@@ -920,10 +920,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>121471860</v>
+        <v>134884157</v>
       </c>
       <c r="C45" t="n">
-        <v>703886</v>
+        <v>702887</v>
       </c>
     </row>
     <row r="46">
@@ -931,10 +931,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>121424469</v>
+        <v>134352414</v>
       </c>
       <c r="C46" t="n">
-        <v>702743</v>
+        <v>702349</v>
       </c>
     </row>
     <row r="47">
@@ -942,10 +942,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>121568469</v>
+        <v>133102258</v>
       </c>
       <c r="C47" t="n">
-        <v>700351</v>
+        <v>692351</v>
       </c>
     </row>
     <row r="48">
@@ -953,10 +953,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>121426349</v>
+        <v>132312807</v>
       </c>
       <c r="C48" t="n">
-        <v>691129</v>
+        <v>685812</v>
       </c>
     </row>
     <row r="49">
@@ -964,10 +964,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>120944864</v>
+        <v>131379757</v>
       </c>
       <c r="C49" t="n">
-        <v>691421</v>
+        <v>674997</v>
       </c>
     </row>
     <row r="50">
@@ -975,10 +975,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>120895705</v>
+        <v>129866217</v>
       </c>
       <c r="C50" t="n">
-        <v>683384</v>
+        <v>669138</v>
       </c>
     </row>
     <row r="51">
@@ -986,10 +986,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>119877273</v>
+        <v>129048669</v>
       </c>
       <c r="C51" t="n">
-        <v>687721</v>
+        <v>655011</v>
       </c>
     </row>
     <row r="52">
@@ -997,10 +997,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>119343380</v>
+        <v>127896191</v>
       </c>
       <c r="C52" t="n">
-        <v>676665</v>
+        <v>653169</v>
       </c>
     </row>
     <row r="53">
@@ -1008,10 +1008,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>118877326</v>
+        <v>126810843</v>
       </c>
       <c r="C53" t="n">
-        <v>683203</v>
+        <v>653265</v>
       </c>
     </row>
     <row r="54">
@@ -1019,10 +1019,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>118128962</v>
+        <v>125861356</v>
       </c>
       <c r="C54" t="n">
-        <v>673689</v>
+        <v>648114</v>
       </c>
     </row>
     <row r="55">
@@ -1030,10 +1030,10 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>117575549</v>
+        <v>125143827</v>
       </c>
       <c r="C55" t="n">
-        <v>663634</v>
+        <v>643878</v>
       </c>
     </row>
   </sheetData>
@@ -1067,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8891280</v>
+        <v>7505043</v>
       </c>
       <c r="C2" t="n">
-        <v>18625</v>
+        <v>17384</v>
       </c>
     </row>
     <row r="3">
@@ -1078,10 +1078,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8760183</v>
+        <v>7589573</v>
       </c>
       <c r="C3" t="n">
-        <v>18149</v>
+        <v>15963</v>
       </c>
     </row>
     <row r="4">
@@ -1089,10 +1089,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>8813908</v>
+        <v>7732794</v>
       </c>
       <c r="C4" t="n">
-        <v>19615</v>
+        <v>16360</v>
       </c>
     </row>
     <row r="5">
@@ -1100,10 +1100,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9154337</v>
+        <v>7877427</v>
       </c>
       <c r="C5" t="n">
-        <v>19043</v>
+        <v>17736</v>
       </c>
     </row>
     <row r="6">
@@ -1111,10 +1111,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9538712</v>
+        <v>8182906</v>
       </c>
       <c r="C6" t="n">
-        <v>18951</v>
+        <v>18604</v>
       </c>
     </row>
     <row r="7">
@@ -1122,10 +1122,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9623657</v>
+        <v>8257774</v>
       </c>
       <c r="C7" t="n">
-        <v>19436</v>
+        <v>19199</v>
       </c>
     </row>
     <row r="8">
@@ -1133,10 +1133,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9964777</v>
+        <v>8506695</v>
       </c>
       <c r="C8" t="n">
-        <v>22373</v>
+        <v>20513</v>
       </c>
     </row>
     <row r="9">
@@ -1144,10 +1144,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10011976</v>
+        <v>8784924</v>
       </c>
       <c r="C9" t="n">
-        <v>21940</v>
+        <v>20501</v>
       </c>
     </row>
     <row r="10">
@@ -1155,10 +1155,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10345312</v>
+        <v>9141904</v>
       </c>
       <c r="C10" t="n">
-        <v>20548</v>
+        <v>22175</v>
       </c>
     </row>
     <row r="11">
@@ -1166,10 +1166,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10561208</v>
+        <v>9236781</v>
       </c>
       <c r="C11" t="n">
-        <v>22142</v>
+        <v>22893</v>
       </c>
     </row>
     <row r="12">
@@ -1177,10 +1177,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10898997</v>
+        <v>9447614</v>
       </c>
       <c r="C12" t="n">
-        <v>23076</v>
+        <v>21136</v>
       </c>
     </row>
     <row r="13">
@@ -1188,10 +1188,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11204833</v>
+        <v>9718024</v>
       </c>
       <c r="C13" t="n">
-        <v>25024</v>
+        <v>23040</v>
       </c>
     </row>
     <row r="14">
@@ -1199,10 +1199,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>11754260</v>
+        <v>10124829</v>
       </c>
       <c r="C14" t="n">
-        <v>26245</v>
+        <v>23804</v>
       </c>
     </row>
     <row r="15">
@@ -1210,10 +1210,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12170536</v>
+        <v>10638135</v>
       </c>
       <c r="C15" t="n">
-        <v>26539</v>
+        <v>26600</v>
       </c>
     </row>
     <row r="16">
@@ -1221,10 +1221,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12610767</v>
+        <v>11137363</v>
       </c>
       <c r="C16" t="n">
-        <v>28569</v>
+        <v>27737</v>
       </c>
     </row>
     <row r="17">
@@ -1232,10 +1232,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12820121</v>
+        <v>11806549</v>
       </c>
       <c r="C17" t="n">
-        <v>29338</v>
+        <v>30858</v>
       </c>
     </row>
     <row r="18">
@@ -1243,10 +1243,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13268565</v>
+        <v>12183493</v>
       </c>
       <c r="C18" t="n">
-        <v>30121</v>
+        <v>31699</v>
       </c>
     </row>
     <row r="19">
@@ -1254,10 +1254,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13535313</v>
+        <v>12653166</v>
       </c>
       <c r="C19" t="n">
-        <v>31835</v>
+        <v>33388</v>
       </c>
     </row>
     <row r="20">
@@ -1265,10 +1265,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>14030654</v>
+        <v>13530055</v>
       </c>
       <c r="C20" t="n">
-        <v>32089</v>
+        <v>37164</v>
       </c>
     </row>
     <row r="21">
@@ -1276,10 +1276,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>14861639</v>
+        <v>14158035</v>
       </c>
       <c r="C21" t="n">
-        <v>34648</v>
+        <v>38704</v>
       </c>
     </row>
     <row r="22">
@@ -1287,10 +1287,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>15726819</v>
+        <v>15093161</v>
       </c>
       <c r="C22" t="n">
-        <v>37563</v>
+        <v>44039</v>
       </c>
     </row>
     <row r="23">
@@ -1298,10 +1298,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>17013483</v>
+        <v>16773919</v>
       </c>
       <c r="C23" t="n">
-        <v>41242</v>
+        <v>48755</v>
       </c>
     </row>
     <row r="24">
@@ -1309,10 +1309,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>18160687</v>
+        <v>18501071</v>
       </c>
       <c r="C24" t="n">
-        <v>44646</v>
+        <v>53969</v>
       </c>
     </row>
     <row r="25">
@@ -1320,10 +1320,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>19610178</v>
+        <v>20459044</v>
       </c>
       <c r="C25" t="n">
-        <v>47964</v>
+        <v>64891</v>
       </c>
     </row>
     <row r="26">
@@ -1331,10 +1331,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>20762394</v>
+        <v>22324829</v>
       </c>
       <c r="C26" t="n">
-        <v>49009</v>
+        <v>68294</v>
       </c>
     </row>
     <row r="27">
@@ -1342,10 +1342,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>22306354</v>
+        <v>24032653</v>
       </c>
       <c r="C27" t="n">
-        <v>56147</v>
+        <v>78841</v>
       </c>
     </row>
     <row r="28">
@@ -1353,10 +1353,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>24229218</v>
+        <v>26018307</v>
       </c>
       <c r="C28" t="n">
-        <v>61760</v>
+        <v>85446</v>
       </c>
     </row>
     <row r="29">
@@ -1364,10 +1364,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>27531630</v>
+        <v>28718034</v>
       </c>
       <c r="C29" t="n">
-        <v>74709</v>
+        <v>96919</v>
       </c>
     </row>
     <row r="30">
@@ -1375,10 +1375,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>31960070</v>
+        <v>33144327</v>
       </c>
       <c r="C30" t="n">
-        <v>89382</v>
+        <v>113922</v>
       </c>
     </row>
     <row r="31">
@@ -1386,10 +1386,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>38243680</v>
+        <v>39377612</v>
       </c>
       <c r="C31" t="n">
-        <v>108722</v>
+        <v>141364</v>
       </c>
     </row>
     <row r="32">
@@ -1397,10 +1397,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>46332926</v>
+        <v>50844565</v>
       </c>
       <c r="C32" t="n">
-        <v>134754</v>
+        <v>195920</v>
       </c>
     </row>
     <row r="33">
@@ -1408,10 +1408,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>53959799</v>
+        <v>65020692</v>
       </c>
       <c r="C33" t="n">
-        <v>159652</v>
+        <v>267695</v>
       </c>
     </row>
     <row r="34">
@@ -1419,10 +1419,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>61911371</v>
+        <v>77518626</v>
       </c>
       <c r="C34" t="n">
-        <v>185446</v>
+        <v>356885</v>
       </c>
     </row>
     <row r="35">
@@ -1430,10 +1430,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>70568552</v>
+        <v>87971277</v>
       </c>
       <c r="C35" t="n">
-        <v>210214</v>
+        <v>446437</v>
       </c>
     </row>
     <row r="36">
@@ -1441,10 +1441,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>83324580</v>
+        <v>97314744</v>
       </c>
       <c r="C36" t="n">
-        <v>260391</v>
+        <v>534462</v>
       </c>
     </row>
     <row r="37">
@@ -1452,10 +1452,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>97432568</v>
+        <v>105459259</v>
       </c>
       <c r="C37" t="n">
-        <v>309112</v>
+        <v>602037</v>
       </c>
     </row>
     <row r="38">
@@ -1463,10 +1463,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>117476075</v>
+        <v>111585290</v>
       </c>
       <c r="C38" t="n">
-        <v>411466</v>
+        <v>667327</v>
       </c>
     </row>
     <row r="39">
@@ -1474,10 +1474,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>132991487</v>
+        <v>115277760</v>
       </c>
       <c r="C39" t="n">
-        <v>508681</v>
+        <v>695596</v>
       </c>
     </row>
     <row r="40">
@@ -1485,10 +1485,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>145193415</v>
+        <v>117596538</v>
       </c>
       <c r="C40" t="n">
-        <v>628549</v>
+        <v>697153</v>
       </c>
     </row>
     <row r="41">
@@ -1496,10 +1496,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>149993066</v>
+        <v>119159986</v>
       </c>
       <c r="C41" t="n">
-        <v>706407</v>
+        <v>696260</v>
       </c>
     </row>
     <row r="42">
@@ -1507,10 +1507,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>151579554</v>
+        <v>120121827</v>
       </c>
       <c r="C42" t="n">
-        <v>763847</v>
+        <v>701437</v>
       </c>
     </row>
     <row r="43">
@@ -1518,10 +1518,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>149803186</v>
+        <v>120631349</v>
       </c>
       <c r="C43" t="n">
-        <v>779812</v>
+        <v>696200</v>
       </c>
     </row>
     <row r="44">
@@ -1529,10 +1529,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>146494089</v>
+        <v>121200180</v>
       </c>
       <c r="C44" t="n">
-        <v>769933</v>
+        <v>705483</v>
       </c>
     </row>
     <row r="45">
@@ -1540,10 +1540,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>142441566</v>
+        <v>121471860</v>
       </c>
       <c r="C45" t="n">
-        <v>765531</v>
+        <v>703886</v>
       </c>
     </row>
     <row r="46">
@@ -1551,10 +1551,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>138218288</v>
+        <v>121424469</v>
       </c>
       <c r="C46" t="n">
-        <v>738345</v>
+        <v>702743</v>
       </c>
     </row>
     <row r="47">
@@ -1562,10 +1562,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>135151136</v>
+        <v>121568469</v>
       </c>
       <c r="C47" t="n">
-        <v>724077</v>
+        <v>700351</v>
       </c>
     </row>
     <row r="48">
@@ -1573,10 +1573,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>133672021</v>
+        <v>121426349</v>
       </c>
       <c r="C48" t="n">
-        <v>716767</v>
+        <v>691129</v>
       </c>
     </row>
     <row r="49">
@@ -1584,10 +1584,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>132676983</v>
+        <v>120944864</v>
       </c>
       <c r="C49" t="n">
-        <v>711605</v>
+        <v>691421</v>
       </c>
     </row>
     <row r="50">
@@ -1595,10 +1595,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>131918859</v>
+        <v>120895705</v>
       </c>
       <c r="C50" t="n">
-        <v>711947</v>
+        <v>683384</v>
       </c>
     </row>
     <row r="51">
@@ -1606,10 +1606,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>132061077</v>
+        <v>119877273</v>
       </c>
       <c r="C51" t="n">
-        <v>702407</v>
+        <v>687721</v>
       </c>
     </row>
     <row r="52">
@@ -1617,10 +1617,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>131187100</v>
+        <v>119343380</v>
       </c>
       <c r="C52" t="n">
-        <v>702169</v>
+        <v>676665</v>
       </c>
     </row>
     <row r="53">
@@ -1628,10 +1628,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>130747333</v>
+        <v>118877326</v>
       </c>
       <c r="C53" t="n">
-        <v>701689</v>
+        <v>683203</v>
       </c>
     </row>
     <row r="54">
@@ -1639,10 +1639,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>130387460</v>
+        <v>118128962</v>
       </c>
       <c r="C54" t="n">
-        <v>695653</v>
+        <v>673689</v>
       </c>
     </row>
     <row r="55">
@@ -1650,10 +1650,10 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>129671556</v>
+        <v>117575549</v>
       </c>
       <c r="C55" t="n">
-        <v>690762</v>
+        <v>663634</v>
       </c>
     </row>
   </sheetData>
@@ -1687,10 +1687,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11120035</v>
+        <v>8891280</v>
       </c>
       <c r="C2" t="n">
-        <v>21545</v>
+        <v>18625</v>
       </c>
     </row>
     <row r="3">
@@ -1698,10 +1698,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11151489</v>
+        <v>8760183</v>
       </c>
       <c r="C3" t="n">
-        <v>22025</v>
+        <v>18149</v>
       </c>
     </row>
     <row r="4">
@@ -1709,10 +1709,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11722767</v>
+        <v>8813908</v>
       </c>
       <c r="C4" t="n">
-        <v>23958</v>
+        <v>19615</v>
       </c>
     </row>
     <row r="5">
@@ -1720,10 +1720,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12091313</v>
+        <v>9154337</v>
       </c>
       <c r="C5" t="n">
-        <v>25665</v>
+        <v>19043</v>
       </c>
     </row>
     <row r="6">
@@ -1731,10 +1731,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12916903</v>
+        <v>9538712</v>
       </c>
       <c r="C6" t="n">
-        <v>27293</v>
+        <v>18951</v>
       </c>
     </row>
     <row r="7">
@@ -1742,10 +1742,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13371175</v>
+        <v>9623657</v>
       </c>
       <c r="C7" t="n">
-        <v>28864</v>
+        <v>19436</v>
       </c>
     </row>
     <row r="8">
@@ -1753,10 +1753,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13846567</v>
+        <v>9964777</v>
       </c>
       <c r="C8" t="n">
-        <v>31744</v>
+        <v>22373</v>
       </c>
     </row>
     <row r="9">
@@ -1764,10 +1764,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14619637</v>
+        <v>10011976</v>
       </c>
       <c r="C9" t="n">
-        <v>32160</v>
+        <v>21940</v>
       </c>
     </row>
     <row r="10">
@@ -1775,10 +1775,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15181894</v>
+        <v>10345312</v>
       </c>
       <c r="C10" t="n">
-        <v>33764</v>
+        <v>20548</v>
       </c>
     </row>
     <row r="11">
@@ -1786,10 +1786,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15739583</v>
+        <v>10561208</v>
       </c>
       <c r="C11" t="n">
-        <v>36875</v>
+        <v>22142</v>
       </c>
     </row>
     <row r="12">
@@ -1797,10 +1797,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16582982</v>
+        <v>10898997</v>
       </c>
       <c r="C12" t="n">
-        <v>39661</v>
+        <v>23076</v>
       </c>
     </row>
     <row r="13">
@@ -1808,10 +1808,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>17676142</v>
+        <v>11204833</v>
       </c>
       <c r="C13" t="n">
-        <v>43460</v>
+        <v>25024</v>
       </c>
     </row>
     <row r="14">
@@ -1819,10 +1819,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>18940932</v>
+        <v>11754260</v>
       </c>
       <c r="C14" t="n">
-        <v>49436</v>
+        <v>26245</v>
       </c>
     </row>
     <row r="15">
@@ -1830,10 +1830,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>21243715</v>
+        <v>12170536</v>
       </c>
       <c r="C15" t="n">
-        <v>55599</v>
+        <v>26539</v>
       </c>
     </row>
     <row r="16">
@@ -1841,10 +1841,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>23324792</v>
+        <v>12610767</v>
       </c>
       <c r="C16" t="n">
-        <v>66375</v>
+        <v>28569</v>
       </c>
     </row>
     <row r="17">
@@ -1852,10 +1852,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>26374060</v>
+        <v>12820121</v>
       </c>
       <c r="C17" t="n">
-        <v>76193</v>
+        <v>29338</v>
       </c>
     </row>
     <row r="18">
@@ -1863,10 +1863,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>30504776</v>
+        <v>13268565</v>
       </c>
       <c r="C18" t="n">
-        <v>88625</v>
+        <v>30121</v>
       </c>
     </row>
     <row r="19">
@@ -1874,10 +1874,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>33682533</v>
+        <v>13535313</v>
       </c>
       <c r="C19" t="n">
-        <v>104345</v>
+        <v>31835</v>
       </c>
     </row>
     <row r="20">
@@ -1885,10 +1885,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>39447744</v>
+        <v>14030654</v>
       </c>
       <c r="C20" t="n">
-        <v>131242</v>
+        <v>32089</v>
       </c>
     </row>
     <row r="21">
@@ -1896,10 +1896,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>47999504</v>
+        <v>14861639</v>
       </c>
       <c r="C21" t="n">
-        <v>166459</v>
+        <v>34648</v>
       </c>
     </row>
     <row r="22">
@@ -1907,10 +1907,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>62339911</v>
+        <v>15726819</v>
       </c>
       <c r="C22" t="n">
-        <v>233632</v>
+        <v>37563</v>
       </c>
     </row>
     <row r="23">
@@ -1918,10 +1918,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>78230154</v>
+        <v>17013483</v>
       </c>
       <c r="C23" t="n">
-        <v>324565</v>
+        <v>41242</v>
       </c>
     </row>
     <row r="24">
@@ -1929,10 +1929,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>90325773</v>
+        <v>18160687</v>
       </c>
       <c r="C24" t="n">
-        <v>425281</v>
+        <v>44646</v>
       </c>
     </row>
     <row r="25">
@@ -1940,10 +1940,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>101414078</v>
+        <v>19610178</v>
       </c>
       <c r="C25" t="n">
-        <v>508923</v>
+        <v>47964</v>
       </c>
     </row>
     <row r="26">
@@ -1951,10 +1951,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>109030262</v>
+        <v>20762394</v>
       </c>
       <c r="C26" t="n">
-        <v>570215</v>
+        <v>49009</v>
       </c>
     </row>
     <row r="27">
@@ -1962,10 +1962,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>115266889</v>
+        <v>22306354</v>
       </c>
       <c r="C27" t="n">
-        <v>631954</v>
+        <v>56147</v>
       </c>
     </row>
     <row r="28">
@@ -1973,10 +1973,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>119421198</v>
+        <v>24229218</v>
       </c>
       <c r="C28" t="n">
-        <v>666254</v>
+        <v>61760</v>
       </c>
     </row>
     <row r="29">
@@ -1984,10 +1984,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>124347187</v>
+        <v>27531630</v>
       </c>
       <c r="C29" t="n">
-        <v>698950</v>
+        <v>74709</v>
       </c>
     </row>
     <row r="30">
@@ -1995,10 +1995,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>128305735</v>
+        <v>31960070</v>
       </c>
       <c r="C30" t="n">
-        <v>709271</v>
+        <v>89382</v>
       </c>
     </row>
     <row r="31">
@@ -2006,10 +2006,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>132597747</v>
+        <v>38243680</v>
       </c>
       <c r="C31" t="n">
-        <v>724329</v>
+        <v>108722</v>
       </c>
     </row>
     <row r="32">
@@ -2017,10 +2017,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>135252053</v>
+        <v>46332926</v>
       </c>
       <c r="C32" t="n">
-        <v>737443</v>
+        <v>134754</v>
       </c>
     </row>
     <row r="33">
@@ -2028,10 +2028,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>136744605</v>
+        <v>53959799</v>
       </c>
       <c r="C33" t="n">
-        <v>743589</v>
+        <v>159652</v>
       </c>
     </row>
     <row r="34">
@@ -2039,10 +2039,10 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>137869222</v>
+        <v>61911371</v>
       </c>
       <c r="C34" t="n">
-        <v>750826</v>
+        <v>185446</v>
       </c>
     </row>
     <row r="35">
@@ -2050,10 +2050,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>138199553</v>
+        <v>70568552</v>
       </c>
       <c r="C35" t="n">
-        <v>747429</v>
+        <v>210214</v>
       </c>
     </row>
     <row r="36">
@@ -2061,10 +2061,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="n">
-        <v>138524853</v>
+        <v>83324580</v>
       </c>
       <c r="C36" t="n">
-        <v>748240</v>
+        <v>260391</v>
       </c>
     </row>
     <row r="37">
@@ -2072,10 +2072,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>138811607</v>
+        <v>97432568</v>
       </c>
       <c r="C37" t="n">
-        <v>752192</v>
+        <v>309112</v>
       </c>
     </row>
     <row r="38">
@@ -2083,10 +2083,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="n">
-        <v>139229583</v>
+        <v>117476075</v>
       </c>
       <c r="C38" t="n">
-        <v>739846</v>
+        <v>411466</v>
       </c>
     </row>
     <row r="39">
@@ -2094,10 +2094,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="n">
-        <v>139198093</v>
+        <v>132991487</v>
       </c>
       <c r="C39" t="n">
-        <v>737904</v>
+        <v>508681</v>
       </c>
     </row>
     <row r="40">
@@ -2105,10 +2105,10 @@
         <v>38</v>
       </c>
       <c r="B40" t="n">
-        <v>138754551</v>
+        <v>145193415</v>
       </c>
       <c r="C40" t="n">
-        <v>728565</v>
+        <v>628549</v>
       </c>
     </row>
     <row r="41">
@@ -2116,10 +2116,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="n">
-        <v>138037649</v>
+        <v>149993066</v>
       </c>
       <c r="C41" t="n">
-        <v>726333</v>
+        <v>706407</v>
       </c>
     </row>
     <row r="42">
@@ -2127,10 +2127,10 @@
         <v>40</v>
       </c>
       <c r="B42" t="n">
-        <v>136897166</v>
+        <v>151579554</v>
       </c>
       <c r="C42" t="n">
-        <v>722908</v>
+        <v>763847</v>
       </c>
     </row>
     <row r="43">
@@ -2138,10 +2138,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="n">
-        <v>136609491</v>
+        <v>149803186</v>
       </c>
       <c r="C43" t="n">
-        <v>714356</v>
+        <v>779812</v>
       </c>
     </row>
     <row r="44">
@@ -2149,10 +2149,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="n">
-        <v>135705317</v>
+        <v>146494089</v>
       </c>
       <c r="C44" t="n">
-        <v>709608</v>
+        <v>769933</v>
       </c>
     </row>
     <row r="45">
@@ -2160,10 +2160,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="n">
-        <v>134884157</v>
+        <v>142441566</v>
       </c>
       <c r="C45" t="n">
-        <v>702887</v>
+        <v>765531</v>
       </c>
     </row>
     <row r="46">
@@ -2171,10 +2171,10 @@
         <v>44</v>
       </c>
       <c r="B46" t="n">
-        <v>134352414</v>
+        <v>138218288</v>
       </c>
       <c r="C46" t="n">
-        <v>702349</v>
+        <v>738345</v>
       </c>
     </row>
     <row r="47">
@@ -2182,10 +2182,10 @@
         <v>45</v>
       </c>
       <c r="B47" t="n">
-        <v>133102258</v>
+        <v>135151136</v>
       </c>
       <c r="C47" t="n">
-        <v>692351</v>
+        <v>724077</v>
       </c>
     </row>
     <row r="48">
@@ -2193,10 +2193,10 @@
         <v>46</v>
       </c>
       <c r="B48" t="n">
-        <v>132312807</v>
+        <v>133672021</v>
       </c>
       <c r="C48" t="n">
-        <v>685812</v>
+        <v>716767</v>
       </c>
     </row>
     <row r="49">
@@ -2204,10 +2204,10 @@
         <v>47</v>
       </c>
       <c r="B49" t="n">
-        <v>131379757</v>
+        <v>132676983</v>
       </c>
       <c r="C49" t="n">
-        <v>674997</v>
+        <v>711605</v>
       </c>
     </row>
     <row r="50">
@@ -2215,10 +2215,10 @@
         <v>48</v>
       </c>
       <c r="B50" t="n">
-        <v>129866217</v>
+        <v>131918859</v>
       </c>
       <c r="C50" t="n">
-        <v>669138</v>
+        <v>711947</v>
       </c>
     </row>
     <row r="51">
@@ -2226,10 +2226,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="n">
-        <v>129048669</v>
+        <v>132061077</v>
       </c>
       <c r="C51" t="n">
-        <v>655011</v>
+        <v>702407</v>
       </c>
     </row>
     <row r="52">
@@ -2237,10 +2237,10 @@
         <v>50</v>
       </c>
       <c r="B52" t="n">
-        <v>127896191</v>
+        <v>131187100</v>
       </c>
       <c r="C52" t="n">
-        <v>653169</v>
+        <v>702169</v>
       </c>
     </row>
     <row r="53">
@@ -2248,10 +2248,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="n">
-        <v>126810843</v>
+        <v>130747333</v>
       </c>
       <c r="C53" t="n">
-        <v>653265</v>
+        <v>701689</v>
       </c>
     </row>
     <row r="54">
@@ -2259,10 +2259,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="n">
-        <v>125861356</v>
+        <v>130387460</v>
       </c>
       <c r="C54" t="n">
-        <v>648114</v>
+        <v>695653</v>
       </c>
     </row>
     <row r="55">
@@ -2270,10 +2270,10 @@
         <v>53</v>
       </c>
       <c r="B55" t="n">
-        <v>125143827</v>
+        <v>129671556</v>
       </c>
       <c r="C55" t="n">
-        <v>643878</v>
+        <v>690762</v>
       </c>
     </row>
   </sheetData>
